--- a/artfynd/S 1685-2025 artfynd.xlsx
+++ b/artfynd/S 1685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82176048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1204,6 +1224,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82176060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1337,6 +1362,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1470,6 +1500,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175886</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1603,6 +1638,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175890</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1733,6 +1773,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107102417</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1866,6 +1911,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82176015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1999,6 +2049,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82176028</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2129,6 +2184,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107102455</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2262,6 +2322,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175983</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2392,6 +2457,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107102435</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2525,6 +2595,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175902</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2658,6 +2733,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175914</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2788,6 +2868,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107102426</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2921,6 +3006,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175956</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3054,6 +3144,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden), Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82175937</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3164,6 +3259,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105241877</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3270,6 +3370,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74471443</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3376,8 +3481,36 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74532267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>